--- a/frontend/public/gen-sticker-docs/originals/05-backlog.xlsx
+++ b/frontend/public/gen-sticker-docs/originals/05-backlog.xlsx
@@ -2,17 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Roadmap" sheetId="1" r:id="R614594f634e94ec7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="2" r:id="Ra15f3b2c10384ebe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposed Sprints" sheetId="3" r:id="R28aabb7231254646"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="4" r:id="R03f23414f6d745a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definition of Done" sheetId="5" r:id="Rf2c006dc07e84fb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priority Dashboard" sheetId="6" r:id="R7e0fce727b77465c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="7" r:id="R7a358a53bb224485"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Workstream" sheetId="8" r:id="R984ffcf8d5344d88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Workstream" sheetId="9" r:id="Rd27eca9251504b44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Workstream" sheetId="10" r:id="R749e3b9617cc4200"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Gates" sheetId="11" r:id="R7f1f1245823149ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Roadmap" sheetId="1" r:id="R1026dfa156cd4624"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="2" r:id="R28c97d2b778a499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposed Sprints" sheetId="3" r:id="Raeb0086bfccf45fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="4" r:id="R6ec9e33e13dc46a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definition of Done" sheetId="5" r:id="R8cf104d39b284267"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priority Dashboard" sheetId="6" r:id="R75740795683b40ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="7" r:id="R804f9994c5f246d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Workstream" sheetId="8" r:id="Rc532edba2cf54ab1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Workstream" sheetId="9" r:id="R1dafbf2056c5406d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Workstream" sheetId="10" r:id="Rfa5e00a0218b4f1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Gates" sheetId="11" r:id="Rbbb7795cfe2f4a23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Face Gate Backlog" sheetId="12" r:id="R72dff027ac574a86"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -447,7 +448,40 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="18">
+  <x:dxfs count="21">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFDC2626"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEE2E2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF92400E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEF3C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF4338CA"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE0E7FF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
     <x:dxf>
       <x:font>
         <x:b/>
@@ -786,13 +820,13 @@
     <xdr:ext cx="11734800" cy="6600825"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="15a9ad3c-69c9-4af7-bc7b-2bcbd518e694"/>
+        <xdr:cNvPr id="1" name="ec2c3479-5863-43aa-966c-3b58a19f057a"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R558038b596ce49c7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R9cc7b31c1f874fb9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -832,7 +866,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R89e06bc9e94e459b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R694a9fc3234d46f0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -866,6 +900,20 @@
     <x:tableColumn id="2" name="Internal demo"/>
     <x:tableColumn id="3" name="Public release"/>
     <x:tableColumn id="4" name="Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="GS0511Table" displayName="GS0511Table" ref="A6:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:E12"/>
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="ID"/>
+    <x:tableColumn id="2" name="Task"/>
+    <x:tableColumn id="3" name="Priority"/>
+    <x:tableColumn id="4" name="Status"/>
+    <x:tableColumn id="5" name="Acceptance"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1213,7 +1261,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Ưu tiên đề xuất từ source audit; không phải cam kết lịch phát hành</x:v>
+        <x:v>Face gate MVP đã có; enforcement, test và telemetry được tách theo giai đoạn</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -1265,7 +1313,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="16" t="str">
-        <x:v>Ba cột Now, Next, Later lần lượt chứa các hạng mục dữ liệu, credentials, durable jobs, schema RLS, test, observability và QA</x:v>
+        <x:v>Now có local MediaPipe gate</x:v>
       </x:c>
       <x:c r="B8" s="16"/>
       <x:c r="C8" s="16"/>
@@ -1273,7 +1321,7 @@
       <x:c r="E8" s="16"/>
       <x:c r="F8" s="16"/>
       <x:c r="I8" s="22" t="str">
-        <x:v>Roadmap đề xuất theo mức độ rủi ro và phụ thuộc kỹ thuật.</x:v>
+        <x:v>Next gồm backend authoritative detector và frontend unit/E2E</x:v>
       </x:c>
       <x:c r="J8" s="22"/>
       <x:c r="K8" s="22"/>
@@ -1359,7 +1407,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="28" t="str">
-        <x:v>Roadmap đề xuất theo mức độ rủi ro và phụ thuộc kỹ thuật.</x:v>
+        <x:v>Later gồm metric false reject, CDN fallback và policy đa khuôn mặt</x:v>
       </x:c>
       <x:c r="B18" s="28"/>
       <x:c r="C18" s="28"/>
@@ -1367,7 +1415,7 @@
       <x:c r="E18" s="28"/>
       <x:c r="F18" s="28"/>
       <x:c r="I18" s="34" t="str">
-        <x:v>Roadmap đề xuất theo mức độ rủi ro và phụ thuộc kỹ thuật.</x:v>
+        <x:v>Roadmap ghi nhận browser face gate đã triển khai và tách rõ phần backend enforcement, test tự động và telemetry còn lại.</x:v>
       </x:c>
       <x:c r="J18" s="34"/>
       <x:c r="K18" s="34"/>
@@ -1453,7 +1501,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="43" t="str">
-        <x:v>Ưu tiên đề xuất từ source audit; không phải cam kết lịch phát hành
+        <x:v>Face gate MVP đã có; enforcement, test và telemetry được tách theo giai đoạn
 Implemented  •  Inferred  •  Gap/Risk  •  Recommended</x:v>
       </x:c>
       <x:c r="B28" s="43"/>
@@ -1536,7 +1584,7 @@
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
       <x:c r="A42" s="45" t="str">
-        <x:v>Hình GS-DOC-05 — Roadmap Now / Next / Later. Roadmap đề xuất theo mức độ rủi ro và phụ thuộc kỹ thuật.</x:v>
+        <x:v>Hình GS-DOC-05 — Roadmap Now / Next / Later. Roadmap ghi nhận browser face gate đã triển khai và tách rõ phần backend enforcement, test tự động và telemetry còn lại.</x:v>
       </x:c>
       <x:c r="B42" s="45"/>
       <x:c r="C42" s="45"/>
@@ -1554,7 +1602,7 @@
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
       <x:c r="A44" s="49" t="str">
-        <x:v>Mô tả sơ đồ: Ba cột Now, Next, Later lần lượt chứa các hạng mục dữ liệu, credentials, durable jobs, schema RLS, test, observability và QA.</x:v>
+        <x:v>Mô tả sơ đồ: Now có local MediaPipe gate; Next gồm backend authoritative detector và frontend unit/E2E; Later gồm metric false reject, CDN fallback và policy đa khuôn mặt.</x:v>
       </x:c>
       <x:c r="B44" s="49"/>
       <x:c r="C44" s="49"/>
@@ -1572,7 +1620,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="51" t="str">
-        <x:v>Nguồn: backend/data/pending_telegram_packs.json; frontend/src/services/authService.ts; backend/migrations/001_add_sticker_pack_soft_delete.sql  •  kien_v5 @ c09e26a  •  2026-08-09</x:v>
+        <x:v>Nguồn: frontend/src/hooks/useImageUpload.ts; frontend/src/workers/faceDetector.worker.ts; frontend/package.json  •  kien_v5 @ 4d23b9a  •  2026-08-10</x:v>
       </x:c>
       <x:c r="B46" s="51"/>
       <x:c r="C46" s="51"/>
@@ -1607,7 +1655,7 @@
   <x:printOptions horizontalCentered="1"/>
   <x:pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd86e78e5cf154ae2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5898037324946e2"/>
 </x:worksheet>
 </file>
 
@@ -1618,7 +1666,7 @@
     <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1642,7 +1690,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-05  •  kien_v5 @ c09e26a  •  2026-08-09  •  Proposed plan</x:v>
+        <x:v>GS-DOC-05  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Proposed plan</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1675,7 +1723,7 @@
         <x:v>Gate</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="7" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A7" s="69" t="str">
         <x:v>TEST-01</x:v>
       </x:c>
@@ -1686,13 +1734,13 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="D7" s="69" t="str">
-        <x:v>Rejected CTA resets upload</x:v>
+        <x:v>Face gate 0/1/&gt;1, timeout, stale/clear</x:v>
       </x:c>
       <x:c r="E7" s="69" t="str">
         <x:v>CI</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="8" ht="54" hidden="0" customHeight="1">
       <x:c r="A8" s="70" t="str">
         <x:v>TEST-02</x:v>
       </x:c>
@@ -1703,7 +1751,7 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="D8" s="70" t="str">
-        <x:v>Auth/upload/poll/gallery/docs</x:v>
+        <x:v>Face reject no POST; auth/upload/poll/gallery/docs</x:v>
       </x:c>
       <x:c r="E8" s="70" t="str">
         <x:v>CI/manual</x:v>
@@ -1774,7 +1822,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c14f3daa28449b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R100e79b064684b27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1807,7 +1855,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-05  •  kien_v5 @ c09e26a  •  2026-08-09  •  Proposed plan</x:v>
+        <x:v>GS-DOC-05  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Proposed plan</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1928,7 +1976,192 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ec2bf0bfbb444f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5b84ebd4cb14fbf"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="27" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="27" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="53" t="str">
+        <x:v>05  /  Implementation Backlog &amp; Sprint Plan</x:v>
+      </x:c>
+      <x:c r="B1" s="53"/>
+      <x:c r="C1" s="53"/>
+      <x:c r="D1" s="53"/>
+      <x:c r="E1" s="53"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="56" t="str">
+        <x:v>Đã triển khai browser MVP và các hạng mục còn lại để chống bypass/đo chất lượng</x:v>
+      </x:c>
+      <x:c r="B2" s="56"/>
+      <x:c r="C2" s="56"/>
+      <x:c r="D2" s="56"/>
+      <x:c r="E2" s="56"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="57" t="str">
+        <x:v>GS-DOC-05  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Proposed plan</x:v>
+      </x:c>
+      <x:c r="B3" s="57"/>
+      <x:c r="C3" s="57"/>
+      <x:c r="D3" s="57"/>
+      <x:c r="E3" s="57"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="58" t="str">
+        <x:v>AS-BUILT • Nội dung viết từ source hiện tại; bộ mẫu chỉ cung cấp cấu trúc trình bày.</x:v>
+      </x:c>
+      <x:c r="B4" s="58"/>
+      <x:c r="C4" s="58"/>
+      <x:c r="D4" s="58"/>
+      <x:c r="E4" s="58"/>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="64" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="B6" s="64" t="str">
+        <x:v>Task</x:v>
+      </x:c>
+      <x:c r="C6" s="64" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="D6" s="64" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="E6" s="64" t="str">
+        <x:v>Acceptance</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A7" s="69" t="str">
+        <x:v>FG-IMP-01</x:v>
+      </x:c>
+      <x:c r="B7" s="69" t="str">
+        <x:v>Browser CPU/WASM exact-one-face gate</x:v>
+      </x:c>
+      <x:c r="C7" s="74" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="D7" s="69" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E7" s="69" t="str">
+        <x:v>0/1/2 browser matrix pass; no GPU/paid API</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A8" s="70" t="str">
+        <x:v>FG-TEST-01</x:v>
+      </x:c>
+      <x:c r="B8" s="70" t="str">
+        <x:v>Unit test service/hook race + timeout</x:v>
+      </x:c>
+      <x:c r="C8" s="74" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="D8" s="70" t="str">
+        <x:v>Next</x:v>
+      </x:c>
+      <x:c r="E8" s="70" t="str">
+        <x:v>Stale/clear/same-file/fail-closed covered</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="54" hidden="0" customHeight="1">
+      <x:c r="A9" s="69" t="str">
+        <x:v>FG-E2E-01</x:v>
+      </x:c>
+      <x:c r="B9" s="69" t="str">
+        <x:v>Browser network assertion</x:v>
+      </x:c>
+      <x:c r="C9" s="74" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="D9" s="69" t="str">
+        <x:v>Next</x:v>
+      </x:c>
+      <x:c r="E9" s="69" t="str">
+        <x:v>Reject path never POSTs /stickers/generate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="54" hidden="0" customHeight="1">
+      <x:c r="A10" s="70" t="str">
+        <x:v>FG-BE-01</x:v>
+      </x:c>
+      <x:c r="B10" s="70" t="str">
+        <x:v>Decide authoritative backend face detector</x:v>
+      </x:c>
+      <x:c r="C10" s="74" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="D10" s="70" t="str">
+        <x:v>Gap</x:v>
+      </x:c>
+      <x:c r="E10" s="70" t="str">
+        <x:v>Direct API policy documented/enforced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A11" s="69" t="str">
+        <x:v>FG-SUPPLY-01</x:v>
+      </x:c>
+      <x:c r="B11" s="69" t="str">
+        <x:v>Self-host/fallback WASM decision</x:v>
+      </x:c>
+      <x:c r="C11" s="76" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="D11" s="69" t="str">
+        <x:v>Later</x:v>
+      </x:c>
+      <x:c r="E11" s="69" t="str">
+        <x:v>CDN incident runbook</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A12" s="70" t="str">
+        <x:v>FG-METRIC-01</x:v>
+      </x:c>
+      <x:c r="B12" s="70" t="str">
+        <x:v>Latency/false-reject metrics</x:v>
+      </x:c>
+      <x:c r="C12" s="76" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="D12" s="70" t="str">
+        <x:v>Later</x:v>
+      </x:c>
+      <x:c r="E12" s="70" t="str">
+        <x:v>TBD thresholds from real telemetry</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A3:E3"/>
+    <x:mergeCell ref="A4:E4"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="C7:C12">
+    <x:cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="P0"/>
+    <x:cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="P1"/>
+    <x:cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="P2"/>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R713f33541a0b42ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1973,7 +2206,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-05  •  kien_v5 @ c09e26a  •  2026-08-09  •  Proposed plan</x:v>
+        <x:v>GS-DOC-05  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Proposed plan</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2425,7 +2658,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d379f40234b4355"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3f53cccafbb4ead"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2461,7 +2694,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-05  •  kien_v5 @ c09e26a  •  2026-08-09  •  Proposed plan</x:v>
+        <x:v>GS-DOC-05  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Proposed plan</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2571,7 +2804,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd82f6738a0554b54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7890ab9f250e41ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2604,7 +2837,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-05  •  kien_v5 @ c09e26a  •  2026-08-09  •  Proposed plan</x:v>
+        <x:v>GS-DOC-05  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Proposed plan</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2711,7 +2944,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73ba3e54d5c1479a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd89c79e3f31b4f5f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2741,7 +2974,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-05  •  kien_v5 @ c09e26a  •  2026-08-09  •  Proposed plan</x:v>
+        <x:v>GS-DOC-05  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Proposed plan</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2839,7 +3072,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6830abe32b3e4b7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c6d9f3e5ff74333"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2873,7 +3106,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-05  •  kien_v5 @ c09e26a  •  2026-08-09  •  Proposed plan</x:v>
+        <x:v>GS-DOC-05  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Proposed plan</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2949,9 +3182,9 @@
     <x:cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="P2"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13d55aba30a74292"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45f4a391621d4e61"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc56e886fcaf4179"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84094e7870834dfd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2990,7 +3223,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-05  •  kien_v5 @ c09e26a  •  2026-08-09  •  Proposed plan</x:v>
+        <x:v>GS-DOC-05  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Proposed plan</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3142,7 +3375,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06ca6182dccf4cd7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb84889ad41d944e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3178,7 +3411,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-05  •  kien_v5 @ c09e26a  •  2026-08-09  •  Proposed plan</x:v>
+        <x:v>GS-DOC-05  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Proposed plan</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3310,7 +3543,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc702ed6480a54fab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fd19754cc804862"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3346,7 +3579,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-05  •  kien_v5 @ c09e26a  •  2026-08-09  •  Proposed plan</x:v>
+        <x:v>GS-DOC-05  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Proposed plan</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3478,7 +3711,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra650be18cac7452b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8053dc0948d04fc8"/>
   </x:tableParts>
 </x:worksheet>
 </file>